--- a/full-data.xlsx
+++ b/full-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asarantsev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A51FDBB6-98A5-4FED-94AA-82069C057A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B579BE06-A10B-4459-9F00-CD5E53EAEEFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>Year</t>
   </si>
@@ -162,14 +162,27 @@
   </si>
   <si>
     <t>FRED series BAA, December daily average, in %</t>
+  </si>
+  <si>
+    <t>Zeros</t>
+  </si>
+  <si>
+    <t>Total returns of 7-year Treasury zero-coupon rates</t>
+  </si>
+  <si>
+    <t>Federal Reserve Research Repository</t>
+  </si>
+  <si>
+    <t>Geometric returns, not in %</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -308,7 +321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -375,6 +388,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,9 +413,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -434,9 +453,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -469,9 +488,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -504,9 +540,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -680,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.140625" style="1" customWidth="1"/>
@@ -688,14 +741,15 @@
     <col min="3" max="3" width="18.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14" style="15" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="15" customWidth="1"/>
     <col min="7" max="7" width="21.85546875" style="13" customWidth="1"/>
     <col min="8" max="8" width="22.42578125" style="10" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="14.7109375" style="28" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -723,8 +777,11 @@
       <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1927</v>
       </c>
@@ -743,8 +800,9 @@
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1928</v>
       </c>
@@ -765,8 +823,9 @@
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="29"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1929</v>
       </c>
@@ -787,8 +846,9 @@
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="29"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1930</v>
       </c>
@@ -809,8 +869,9 @@
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="29"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1931</v>
       </c>
@@ -831,8 +892,9 @@
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="29"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1932</v>
       </c>
@@ -853,8 +915,9 @@
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1933</v>
       </c>
@@ -875,8 +938,9 @@
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1934</v>
       </c>
@@ -897,8 +961,9 @@
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>1935</v>
       </c>
@@ -919,8 +984,9 @@
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="29"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1936</v>
       </c>
@@ -941,8 +1007,9 @@
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>1937</v>
       </c>
@@ -963,8 +1030,9 @@
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="29"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>1938</v>
       </c>
@@ -985,8 +1053,9 @@
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" s="29"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1939</v>
       </c>
@@ -1007,8 +1076,9 @@
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="29"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>1940</v>
       </c>
@@ -1029,8 +1099,9 @@
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" s="29"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>1941</v>
       </c>
@@ -1051,8 +1122,9 @@
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16" s="29"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>1942</v>
       </c>
@@ -1073,8 +1145,9 @@
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J17" s="29"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>1943</v>
       </c>
@@ -1095,8 +1168,9 @@
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J18" s="29"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>1944</v>
       </c>
@@ -1117,8 +1191,9 @@
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J19" s="29"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>1945</v>
       </c>
@@ -1139,8 +1214,9 @@
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J20" s="29"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>1946</v>
       </c>
@@ -1161,8 +1237,9 @@
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21" s="29"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>1947</v>
       </c>
@@ -1183,8 +1260,9 @@
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J22" s="29"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>1948</v>
       </c>
@@ -1205,8 +1283,9 @@
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J23" s="29"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>1949</v>
       </c>
@@ -1227,8 +1306,9 @@
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>1950</v>
       </c>
@@ -1249,8 +1329,9 @@
       </c>
       <c r="G25" s="11"/>
       <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>1951</v>
       </c>
@@ -1271,8 +1352,9 @@
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="8"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>1952</v>
       </c>
@@ -1293,8 +1375,9 @@
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>1953</v>
       </c>
@@ -1315,8 +1398,9 @@
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="8"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J28" s="29"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>1954</v>
       </c>
@@ -1337,8 +1421,9 @@
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J29" s="29"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>1955</v>
       </c>
@@ -1359,8 +1444,9 @@
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="8"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>1956</v>
       </c>
@@ -1381,8 +1467,9 @@
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J31" s="29"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>1957</v>
       </c>
@@ -1403,8 +1490,9 @@
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="8"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J32" s="29"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>1958</v>
       </c>
@@ -1425,8 +1513,9 @@
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J33" s="29"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>1959</v>
       </c>
@@ -1447,8 +1536,9 @@
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J34" s="29"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>1960</v>
       </c>
@@ -1469,8 +1559,9 @@
       </c>
       <c r="G35" s="11"/>
       <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J35" s="29"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>1961</v>
       </c>
@@ -1491,8 +1582,9 @@
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J36" s="29"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>1962</v>
       </c>
@@ -1513,8 +1605,11 @@
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J37" s="28">
+        <v>5.6351000000000012E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>1963</v>
       </c>
@@ -1535,8 +1630,11 @@
       </c>
       <c r="G38" s="11"/>
       <c r="H38" s="8"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J38" s="28">
+        <v>1.709299999999999E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>1964</v>
       </c>
@@ -1557,8 +1655,11 @@
       </c>
       <c r="G39" s="11"/>
       <c r="H39" s="8"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J39" s="28">
+        <v>3.7941000000000003E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>1965</v>
       </c>
@@ -1579,8 +1680,11 @@
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="8"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J40" s="28">
+        <v>1.5509999999999736E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>1966</v>
       </c>
@@ -1601,8 +1705,11 @@
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J41" s="28">
+        <v>5.0431999999999991E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>1967</v>
       </c>
@@ -1623,8 +1730,11 @@
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J42" s="28">
+        <v>-1.204899999999995E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>1968</v>
       </c>
@@ -1645,8 +1755,11 @@
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J43" s="28">
+        <v>3.1112000000000039E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>1969</v>
       </c>
@@ -1667,8 +1780,11 @@
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="8"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J44" s="28">
+        <v>-2.6492999999999968E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>1970</v>
       </c>
@@ -1691,8 +1807,11 @@
       <c r="H45" s="9">
         <v>-9.9412E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J45" s="28">
+        <v>0.15857999999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>1971</v>
       </c>
@@ -1715,8 +1834,11 @@
       <c r="H46" s="9">
         <v>0.33241599999999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J46" s="28">
+        <v>8.9775999999999953E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>1972</v>
       </c>
@@ -1741,8 +1863,11 @@
       <c r="H47" s="9">
         <v>0.33558399999999999</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J47" s="28">
+        <v>3.0604000000000013E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>1973</v>
       </c>
@@ -1767,8 +1892,11 @@
       <c r="H48" s="9">
         <v>-0.15588399999999997</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48" s="28">
+        <v>3.4935000000000042E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>1974</v>
       </c>
@@ -1793,8 +1921,11 @@
       <c r="H49" s="9">
         <v>-0.25567599999999996</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" s="28">
+        <v>3.980999999999995E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>1975</v>
       </c>
@@ -1819,8 +1950,11 @@
       <c r="H50" s="9">
         <v>0.46570400000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50" s="28">
+        <v>5.3751999999999994E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>1976</v>
       </c>
@@ -1845,8 +1979,11 @@
       <c r="H51" s="9">
         <v>1.7864000000000005E-2</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" s="28">
+        <v>0.14549700000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>1977</v>
       </c>
@@ -1871,8 +2008,11 @@
       <c r="H52" s="9">
         <v>0.240892</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52" s="28">
+        <v>1.9469999999999744E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>1978</v>
       </c>
@@ -1897,8 +2037,11 @@
       <c r="H53" s="9">
         <v>0.31946799999999997</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53" s="28">
+        <v>-7.5849999999999798E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>1979</v>
       </c>
@@ -1923,8 +2066,11 @@
       <c r="H54" s="9">
         <v>8.1108E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" s="28">
+        <v>2.8382000000000004E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>1980</v>
       </c>
@@ -1949,8 +2095,11 @@
       <c r="H55" s="9">
         <v>0.26483199999999996</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55" s="28">
+        <v>-2.3611999999999966E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>1981</v>
       </c>
@@ -1975,8 +2124,11 @@
       <c r="H56" s="9">
         <v>-2.1712000000000002E-2</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56" s="28">
+        <v>2.4958999999999919E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>1982</v>
       </c>
@@ -2001,8 +2153,11 @@
       <c r="H57" s="9">
         <v>3.6639999999999989E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57" s="28">
+        <v>0.32143699999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>1983</v>
       </c>
@@ -2027,8 +2182,11 @@
       <c r="H58" s="9">
         <v>0.23741199999999998</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58" s="28">
+        <v>4.3760999999999939E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>1984</v>
       </c>
@@ -2053,8 +2211,11 @@
       <c r="H59" s="9">
         <v>7.6032000000000002E-2</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J59" s="28">
+        <v>0.13476700000000008</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>1985</v>
       </c>
@@ -2079,8 +2240,11 @@
       <c r="H60" s="9">
         <v>0.56276000000000004</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60" s="28">
+        <v>0.26802700000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>1986</v>
       </c>
@@ -2105,8 +2269,11 @@
       <c r="H61" s="9">
         <v>0.64781200000000005</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" s="28">
+        <v>0.19629599999999997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>1987</v>
       </c>
@@ -2131,8 +2298,11 @@
       <c r="H62" s="9">
         <v>0.261492</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J62" s="28">
+        <v>-7.5939584034599508E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>1988</v>
       </c>
@@ -2160,8 +2330,11 @@
       <c r="I63" s="2">
         <v>0.40429999999999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63" s="28">
+        <v>6.610516061036989E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>1989</v>
       </c>
@@ -2189,8 +2362,11 @@
       <c r="I64" s="2">
         <v>0.64959999999999996</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" s="28">
+        <v>0.16040665255153003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>1990</v>
       </c>
@@ -2218,8 +2394,11 @@
       <c r="I65" s="2">
         <v>-0.10550000000000001</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" s="28">
+        <v>8.1349363711299957E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>1991</v>
       </c>
@@ -2247,8 +2426,11 @@
       <c r="I66" s="2">
         <v>0.59909999999999997</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66" s="28">
+        <v>0.17430252490858997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>1992</v>
       </c>
@@ -2276,8 +2458,11 @@
       <c r="I67" s="2">
         <v>0.114</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J67" s="28">
+        <v>7.8166628555629961E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>1993</v>
       </c>
@@ -2305,8 +2490,11 @@
       <c r="I68" s="2">
         <v>0.74840000000000007</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J68" s="28">
+        <v>0.13949820763897997</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>1994</v>
       </c>
@@ -2334,8 +2522,11 @@
       <c r="I69" s="2">
         <v>-7.3200000000000001E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J69" s="28">
+        <v>-7.158837379663005E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>1995</v>
       </c>
@@ -2363,8 +2554,11 @@
       <c r="I70" s="2">
         <v>-5.21E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J70" s="28">
+        <v>0.21905643953991999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>1996</v>
       </c>
@@ -2392,8 +2586,11 @@
       <c r="I71" s="2">
         <v>6.0299999999999999E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J71" s="28">
+        <v>1.126746741321007E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>1997</v>
       </c>
@@ -2421,8 +2618,11 @@
       <c r="I72" s="2">
         <v>-0.1159</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72" s="28">
+        <v>9.8774454586029986E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>1998</v>
       </c>
@@ -2450,8 +2650,11 @@
       <c r="I73" s="2">
         <v>-0.25340000000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J73" s="28">
+        <v>0.11547331814562001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>1999</v>
       </c>
@@ -2479,8 +2682,11 @@
       <c r="I74" s="2">
         <v>0.66409999999999991</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J74" s="28">
+        <v>-5.1010380404390009E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>2000</v>
       </c>
@@ -2508,8 +2714,11 @@
       <c r="I75" s="2">
         <v>-0.30609999999999998</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J75" s="28">
+        <v>0.15019220753235998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>2001</v>
       </c>
@@ -2537,8 +2746,11 @@
       <c r="I76" s="2">
         <v>-2.3700000000000002E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J76" s="28">
+        <v>7.1269448927470058E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>2002</v>
       </c>
@@ -2566,8 +2778,11 @@
       <c r="I77" s="2">
         <v>-0.06</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J77" s="28">
+        <v>0.16191900000000009</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>2003</v>
       </c>
@@ -2595,8 +2810,11 @@
       <c r="I78" s="2">
         <v>0.56279999999999997</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J78" s="28">
+        <v>3.0352999999999995E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>2004</v>
       </c>
@@ -2624,8 +2842,11 @@
       <c r="I79" s="2">
         <v>0.25950000000000001</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J79" s="28">
+        <v>4.3900000000000008E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>2005</v>
       </c>
@@ -2653,8 +2874,11 @@
       <c r="I80" s="2">
         <v>0.34539999999999998</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80" s="28">
+        <v>1.9120999999999989E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>2006</v>
       </c>
@@ -2682,8 +2906,11 @@
       <c r="I81" s="2">
         <v>0.32549999999999996</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" s="28">
+        <v>2.6270000000000026E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>2007</v>
       </c>
@@ -2711,8 +2938,11 @@
       <c r="I82" s="2">
         <v>0.3982</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J82" s="28">
+        <v>0.10578800000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>2008</v>
       </c>
@@ -2740,8 +2970,11 @@
       <c r="I83" s="2">
         <v>-0.53180000000000005</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J83" s="28">
+        <v>0.15531600159072903</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>2009</v>
       </c>
@@ -2769,8 +3002,11 @@
       <c r="I84" s="2">
         <v>0.79020000000000001</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J84" s="28">
+        <v>-3.1261987686156782E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>2010</v>
       </c>
@@ -2798,8 +3034,11 @@
       <c r="I85" s="2">
         <v>0.192</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J85" s="28">
+        <v>9.519499778747563E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>2011</v>
       </c>
@@ -2827,8 +3066,11 @@
       <c r="I86" s="2">
         <v>-0.18170000000000003</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J86" s="28">
+        <v>0.1266109943389889</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>2012</v>
       </c>
@@ -2856,8 +3098,11 @@
       <c r="I87" s="2">
         <v>0.18629999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J87" s="28">
+        <v>3.7120003700256386E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>2013</v>
       </c>
@@ -2885,8 +3130,11 @@
       <c r="I88" s="2">
         <v>-2.2700000000000001E-2</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J88" s="28">
+        <v>-4.6272001266479491E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>2014</v>
       </c>
@@ -2914,8 +3162,11 @@
       <c r="I89" s="2">
         <v>-1.8200000000000001E-2</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J89" s="28">
+        <v>6.3026988506316925E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>2015</v>
       </c>
@@ -2943,8 +3194,11 @@
       <c r="I90" s="2">
         <v>-0.14599999999999999</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J90" s="28">
+        <v>2.2270002365112181E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>2016</v>
       </c>
@@ -2972,8 +3226,11 @@
       <c r="I91" s="2">
         <v>0.11599999999999999</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J91" s="28">
+        <v>1.7978999614716003E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>2017</v>
       </c>
@@ -3001,8 +3258,11 @@
       <c r="I92" s="2">
         <v>0.3775</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J92" s="28">
+        <v>2.4370000362395922E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>2018</v>
       </c>
@@ -3030,8 +3290,11 @@
       <c r="I93" s="2">
         <v>-0.14249999999999999</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J93" s="28">
+        <v>9.5059990882872831E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>2019</v>
       </c>
@@ -3059,8 +3322,11 @@
       <c r="I94" s="2">
         <v>0.1888</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J94" s="28">
+        <v>7.5331003665924504E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>2020</v>
       </c>
@@ -3088,8 +3354,11 @@
       <c r="I95" s="2">
         <v>0.18690000000000001</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J95" s="28">
+        <v>9.650599798393282E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>2021</v>
       </c>
@@ -3117,8 +3386,11 @@
       <c r="I96" s="2">
         <v>-2.2200000000000001E-2</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J96" s="28">
+        <v>-3.7816999999999996E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>2022</v>
       </c>
@@ -3146,8 +3418,11 @@
       <c r="I97" s="2">
         <v>-0.19739999999999999</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J97" s="28">
+        <v>-0.13447699999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>2023</v>
       </c>
@@ -3175,8 +3450,11 @@
       <c r="I98" s="2">
         <v>0.1027</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J98" s="28">
+        <v>4.214399999999998E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>2024</v>
       </c>
@@ -3204,8 +3482,11 @@
       <c r="I99" s="2">
         <v>8.0500000000000002E-2</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J99" s="28">
+        <v>4.1639999999999941E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>2025</v>
       </c>
@@ -3233,10 +3514,13 @@
       <c r="I100" s="2">
         <v>0.34360000000000002</v>
       </c>
+      <c r="J100" s="28">
+        <v>8.2027000000000044E-2</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A88:A181">
-    <sortCondition ref="A88:A181"/>
+  <sortState ref="A123:A216">
+    <sortCondition ref="A123:A216"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3245,7 +3529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C470D53-A55D-47EE-B2CB-A39FEC9CFC57}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" style="17" customWidth="1"/>
@@ -3448,6 +3732,23 @@
         <v>44</v>
       </c>
     </row>
+    <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
